--- a/Aula 04/Exemplo.xlsx
+++ b/Aula 04/Exemplo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reenye\Documents\SENAI\Excel Básico\Excel-Basico\Aula 04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reenye\Documents\Excel-Basico\Aula 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24582A35-E2E7-4106-8B2A-0B28D4714990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E102BEA3-A921-46D2-960F-C49DE4BDDF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5E32D5F6-3309-4D72-B9D4-A61546E9CCCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E32D5F6-3309-4D72-B9D4-A61546E9CCCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Nome</t>
   </si>
@@ -96,6 +96,21 @@
   </si>
   <si>
     <t>João</t>
+  </si>
+  <si>
+    <t>Nome Completo</t>
+  </si>
+  <si>
+    <t>Nome Formatado</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Nome Minusculo</t>
+  </si>
+  <si>
+    <t>Sobrenome Minusculo</t>
   </si>
 </sst>
 </file>
@@ -139,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -149,6 +164,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,13 +501,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0E22AF-1B02-4739-8E61-20FBD18770E3}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -503,7 +522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -517,7 +536,7 @@
         <v>38791</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -531,7 +550,7 @@
         <v>36394</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -545,7 +564,7 @@
         <v>38362</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -559,7 +578,7 @@
         <v>35008</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -573,7 +592,141 @@
         <v>32324</v>
       </c>
     </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>_xlfn.TEXTJOIN(" ",TRUE,A2:B2)</f>
+        <v>João silva</v>
+      </c>
+      <c r="B10" t="str">
+        <f>PROPER(A10)</f>
+        <v>João Silva</v>
+      </c>
+      <c r="C10" t="str">
+        <f>LOWER(A2)</f>
+        <v>joão</v>
+      </c>
+      <c r="D10" t="str">
+        <f>LOWER(B2)</f>
+        <v>silva</v>
+      </c>
+      <c r="E10" t="str">
+        <f>_xlfn.TEXTJOIN(".",TRUE,C10:D10)</f>
+        <v>joão.silva</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f t="shared" ref="A11:A14" si="0">_xlfn.TEXTJOIN(" ",TRUE,A3:B3)</f>
+        <v>MARIA SOUZA</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" ref="B11:B15" si="1">PROPER(A11)</f>
+        <v>Maria Souza</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" ref="C11:C14" si="2">LOWER(A3)</f>
+        <v>maria</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" ref="D11:D14" si="3">LOWER(B3)</f>
+        <v>souza</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" ref="E11:E14" si="4">_xlfn.TEXTJOIN(".",TRUE,C11:D11)</f>
+        <v>maria.souza</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f t="shared" si="0"/>
+        <v>carlos Pereira</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="1"/>
+        <v>Carlos Pereira</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="2"/>
+        <v>carlos</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="3"/>
+        <v>pereira</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="4"/>
+        <v>carlos.pereira</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>ana lima</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="1"/>
+        <v>Ana Lima</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="2"/>
+        <v>ana</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="3"/>
+        <v>lima</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="4"/>
+        <v>ana.lima</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>ROBERTO ALVES</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="1"/>
+        <v>Roberto Alves</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="2"/>
+        <v>roberto</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="3"/>
+        <v>alves</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="4"/>
+        <v>roberto.alves</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Aula 04/Exemplo.xlsx
+++ b/Aula 04/Exemplo.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reenye\Documents\Excel-Basico\Aula 04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E102BEA3-A921-46D2-960F-C49DE4BDDF68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAE1F8E-4657-4608-8CD6-4027FE5D83D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E32D5F6-3309-4D72-B9D4-A61546E9CCCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,14 +33,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Nome</t>
   </si>
@@ -111,6 +112,33 @@
   </si>
   <si>
     <t>Sobrenome Minusculo</t>
+  </si>
+  <si>
+    <t>Fulano</t>
+  </si>
+  <si>
+    <t>Silva</t>
+  </si>
+  <si>
+    <t>Rua Sem Saida</t>
+  </si>
+  <si>
+    <t>Jd das Avenidas</t>
+  </si>
+  <si>
+    <t>Jaguariuna</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Cadastros Sem Documento</t>
+  </si>
+  <si>
+    <t>Numero de Cadastros</t>
+  </si>
+  <si>
+    <t>Idade</t>
   </si>
 </sst>
 </file>
@@ -154,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -167,11 +195,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -501,14 +566,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0E22AF-1B02-4739-8E61-20FBD18770E3}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -521,8 +589,15 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -535,8 +610,20 @@
       <c r="D2" s="3">
         <v>38791</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>12345678900</v>
+      </c>
+      <c r="F2">
+        <f>LEN(E2)</f>
+        <v>11</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2">
+        <f ca="1">DATEDIF(D2,TODAY(),"Y")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -549,8 +636,20 @@
       <c r="D3" s="3">
         <v>36394</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>1232484651</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F6" si="0">LEN(E3)</f>
+        <v>10</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3">
+        <f t="shared" ref="H3:H6" ca="1" si="1">DATEDIF(D3,TODAY(),"Y")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -563,8 +662,18 @@
       <c r="D4" s="2">
         <v>38362</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="6"/>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4">
+        <f t="shared" ca="1" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -577,8 +686,20 @@
       <c r="D5" s="3">
         <v>35008</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>12345678900</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5">
+        <f t="shared" ca="1" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -591,8 +712,33 @@
       <c r="D6" s="3">
         <v>32324</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6">
+        <f t="shared" ca="1" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="7">
+        <f>COUNTA(A2:A6)</f>
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <f>G8-G9</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
@@ -608,8 +754,15 @@
       <c r="E9" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="7">
+        <f>COUNTBLANK(E2:E6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>_xlfn.TEXTJOIN(" ",TRUE,A2:B2)</f>
         <v>João silva</v>
@@ -627,106 +780,161 @@
         <v>silva</v>
       </c>
       <c r="E10" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,C10:D10)</f>
-        <v>joão.silva</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <f>_xlfn.TEXTJOIN(".",TRUE,C10:D10) &amp; "@senaisp.edu.br"</f>
+        <v>joão.silva@senaisp.edu.br</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
-        <f t="shared" ref="A11:A14" si="0">_xlfn.TEXTJOIN(" ",TRUE,A3:B3)</f>
+        <f t="shared" ref="A11:A14" si="2">_xlfn.TEXTJOIN(" ",TRUE,A3:B3)</f>
         <v>MARIA SOUZA</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" ref="B11:B15" si="1">PROPER(A11)</f>
+        <f t="shared" ref="B11:B15" si="3">PROPER(A11)</f>
         <v>Maria Souza</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" ref="C11:C14" si="2">LOWER(A3)</f>
+        <f t="shared" ref="C11:C14" si="4">LOWER(A3)</f>
         <v>maria</v>
       </c>
       <c r="D11" t="str">
-        <f t="shared" ref="D11:D14" si="3">LOWER(B3)</f>
+        <f t="shared" ref="D11:D14" si="5">LOWER(B3)</f>
         <v>souza</v>
       </c>
       <c r="E11" t="str">
-        <f t="shared" ref="E11:E14" si="4">_xlfn.TEXTJOIN(".",TRUE,C11:D11)</f>
-        <v>maria.souza</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="E11:E14" si="6">_xlfn.TEXTJOIN(".",TRUE,C11:D11) &amp; "@senaisp.edu.br"</f>
+        <v>maria.souza@senaisp.edu.br</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>carlos Pereira</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>Carlos Pereira</v>
       </c>
       <c r="C12" t="str">
+        <f t="shared" si="4"/>
+        <v>carlos</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="5"/>
+        <v>pereira</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="6"/>
+        <v>carlos.pereira@senaisp.edu.br</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
         <f t="shared" si="2"/>
-        <v>carlos</v>
-      </c>
-      <c r="D12" t="str">
+        <v>ana lima</v>
+      </c>
+      <c r="B13" t="str">
         <f t="shared" si="3"/>
-        <v>pereira</v>
-      </c>
-      <c r="E12" t="str">
+        <v>Ana Lima</v>
+      </c>
+      <c r="C13" t="str">
         <f t="shared" si="4"/>
-        <v>carlos.pereira</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f t="shared" si="0"/>
-        <v>ana lima</v>
-      </c>
-      <c r="B13" t="str">
-        <f t="shared" si="1"/>
-        <v>Ana Lima</v>
-      </c>
-      <c r="C13" t="str">
+        <v>ana</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="5"/>
+        <v>lima</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="6"/>
+        <v>ana.lima@senaisp.edu.br</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
         <f t="shared" si="2"/>
-        <v>ana</v>
-      </c>
-      <c r="D13" t="str">
+        <v>ROBERTO ALVES</v>
+      </c>
+      <c r="B14" t="str">
         <f t="shared" si="3"/>
-        <v>lima</v>
-      </c>
-      <c r="E13" t="str">
+        <v>Roberto Alves</v>
+      </c>
+      <c r="C14" t="str">
         <f t="shared" si="4"/>
-        <v>ana.lima</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
-        <f t="shared" si="0"/>
-        <v>ROBERTO ALVES</v>
-      </c>
-      <c r="B14" t="str">
-        <f t="shared" si="1"/>
-        <v>Roberto Alves</v>
-      </c>
-      <c r="C14" t="str">
-        <f t="shared" si="2"/>
         <v>roberto</v>
       </c>
       <c r="D14" t="str">
+        <f t="shared" si="5"/>
+        <v>alves</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="6"/>
+        <v>roberto.alves@senaisp.edu.br</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="str">
         <f t="shared" si="3"/>
-        <v>alves</v>
-      </c>
-      <c r="E14" t="str">
-        <f t="shared" si="4"/>
-        <v>roberto.alves</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>11</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>11</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF2C74A-3D3E-448B-AA73-0EAF39B66399}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="str">
+        <f>A1 &amp; " " &amp; B1</f>
+        <v>Fulano Silva</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f>_xlfn.TEXTJOIN(",",TRUE,A3:D3)</f>
+        <v>Rua Sem Saida,35,Jd das Avenidas,Jaguariuna</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>